--- a/padronizador-c3b/tests/fixtures/Matriz_BYD_estrutura_real_sintetica.xlsx
+++ b/padronizador-c3b/tests/fixtures/Matriz_BYD_estrutura_real_sintetica.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="SA6H" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Exemplo 范例" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="BASE DE DADOS" state="visible" r:id="rId6"/>
+    <sheet sheetId="2" name="HA2H" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Exemplo 范例" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="BASE DE DADOS" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="33">
   <si>
     <t xml:space="preserve">Divisão 11 
 第十一事业部 </t>
@@ -80,6 +81,9 @@
   </si>
   <si>
     <t>01/09/2026</t>
+  </si>
+  <si>
+    <t>XYZ</t>
   </si>
   <si>
     <t>2</t>
@@ -115,6 +119,9 @@
     <t xml:space="preserve">Definição  定义：
 i: Fase de treinamento. …
 L: Fase de trabalho. …</t>
+  </si>
+  <si>
+    <t>PEDRO EXEMPLO ALVSE</t>
   </si>
   <si>
     <t xml:space="preserve">Modelo
@@ -1203,7 +1210,9 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
-      <c r="T9" s="3"/>
+      <c r="T9" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
       <c r="X9" s="3"/>
@@ -1298,10 +1307,10 @@
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -1412,10 +1421,10 @@
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -1526,10 +1535,10 @@
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -1544,7 +1553,7 @@
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
       <c r="T21" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
@@ -1642,7 +1651,7 @@
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B25"/>
       <c r="C25">
@@ -1672,10 +1681,10 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1778,7 +1787,7 @@
         <v>9</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="W5" s="1" t="s">
         <v>11</v>
@@ -1855,7 +1864,9 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
-      <c r="T9" s="3"/>
+      <c r="T9" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
       <c r="X9" s="3"/>
@@ -1950,10 +1961,10 @@
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -2064,10 +2075,10 @@
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -2178,10 +2189,10 @@
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -2196,7 +2207,7 @@
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
       <c r="T21" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
@@ -2294,7 +2305,7 @@
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B25"/>
       <c r="C25">
@@ -2311,7 +2322,7 @@
       </c>
       <c r="O25">
         <f>SUM(Q11+Q15+Q19+Q23)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S25">
         <f>SUM(U11+U15+U19+U23)</f>
@@ -2324,10 +2335,10 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2376,17 +2387,670 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:AA26"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" t="s">
+        <v>2</v>
+      </c>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="19:26" x14ac:dyDescent="0.25">
+      <c r="S3"/>
+      <c r="T3"/>
+      <c r="U3"/>
+      <c r="V3"/>
+      <c r="W3"/>
+      <c r="X3"/>
+      <c r="Y3"/>
+      <c r="Z3"/>
+    </row>
+    <row r="5" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7"/>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L7" t="s">
+        <v>14</v>
+      </c>
+      <c r="O7" t="s">
+        <v>13</v>
+      </c>
+      <c r="P7" t="s">
+        <v>14</v>
+      </c>
+      <c r="S7" t="s">
+        <v>13</v>
+      </c>
+      <c r="T7" t="s">
+        <v>14</v>
+      </c>
+      <c r="W7" t="s">
+        <v>13</v>
+      </c>
+      <c r="X7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8"/>
+      <c r="B8"/>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="T9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="U9" s="3"/>
+      <c r="V9" s="3"/>
+      <c r="X9" s="3"/>
+      <c r="Y9" s="3"/>
+      <c r="Z9" s="3"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10"/>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10"/>
+      <c r="T10" s="3"/>
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
+      <c r="W10"/>
+      <c r="X10" s="3"/>
+      <c r="Y10" s="3"/>
+      <c r="Z10" s="3"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11"/>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="4">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+      <c r="W11"/>
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12"/>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
+      <c r="W12"/>
+      <c r="X12" s="3"/>
+      <c r="Y12" s="3"/>
+      <c r="Z12" s="3"/>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="T13" s="3"/>
+      <c r="U13" s="3"/>
+      <c r="V13" s="3"/>
+      <c r="X13" s="3"/>
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="3"/>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14"/>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14"/>
+      <c r="T14" s="3"/>
+      <c r="U14" s="3"/>
+      <c r="V14" s="3"/>
+      <c r="W14"/>
+      <c r="X14" s="3"/>
+      <c r="Y14" s="3"/>
+      <c r="Z14" s="3"/>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15"/>
+      <c r="B15"/>
+      <c r="C15"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="6">
+        <v>1</v>
+      </c>
+      <c r="F15" s="5"/>
+      <c r="G15"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="4">
+        <v>1</v>
+      </c>
+      <c r="R15" s="2"/>
+      <c r="S15"/>
+      <c r="T15" s="3"/>
+      <c r="U15" s="3"/>
+      <c r="V15" s="3"/>
+      <c r="W15"/>
+      <c r="X15" s="3"/>
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="3"/>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16"/>
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16"/>
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+      <c r="W16"/>
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+      <c r="T17" s="3"/>
+      <c r="U17" s="3"/>
+      <c r="V17" s="3"/>
+      <c r="X17" s="3"/>
+      <c r="Y17" s="3"/>
+      <c r="Z17" s="3"/>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A18"/>
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="S18"/>
+      <c r="T18" s="3"/>
+      <c r="U18" s="3"/>
+      <c r="V18" s="3"/>
+      <c r="W18"/>
+      <c r="X18" s="3"/>
+      <c r="Y18" s="3"/>
+      <c r="Z18" s="3"/>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A19"/>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="4">
+        <v>1</v>
+      </c>
+      <c r="J19" s="2"/>
+      <c r="K19"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="4">
+        <v>1</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+      <c r="W19"/>
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A20"/>
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
+      <c r="W20"/>
+      <c r="X20" s="3"/>
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="3"/>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+      <c r="T21" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="U21" s="7"/>
+      <c r="V21" s="7"/>
+      <c r="X21" s="2"/>
+      <c r="Y21" s="2"/>
+      <c r="Z21" s="2"/>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22"/>
+      <c r="T22" s="7"/>
+      <c r="U22" s="7"/>
+      <c r="V22" s="7"/>
+      <c r="W22"/>
+      <c r="X22" s="2"/>
+      <c r="Y22" s="2"/>
+      <c r="Z22" s="2"/>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="8">
+        <v>1</v>
+      </c>
+      <c r="V23" s="7"/>
+      <c r="W23"/>
+      <c r="X23" s="2"/>
+      <c r="Y23" s="4">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="2"/>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24"/>
+      <c r="T24" s="7"/>
+      <c r="U24" s="7"/>
+      <c r="V24" s="7"/>
+      <c r="W24"/>
+      <c r="X24" s="2"/>
+      <c r="Y24" s="2"/>
+      <c r="Z24" s="2"/>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25"/>
+      <c r="C25">
+        <f>SUM(E11+E15+E19+E23)</f>
+        <v>2</v>
+      </c>
+      <c r="G25">
+        <f>SUM(I11+I15+I19+I23)</f>
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <f>SUM(M11+M15+M19+M23)</f>
+        <v>1</v>
+      </c>
+      <c r="O25">
+        <f>SUM(Q11+Q15+Q19+Q23)</f>
+        <v>1</v>
+      </c>
+      <c r="S25">
+        <f>SUM(U11+U15+U19+U23)</f>
+        <v>1</v>
+      </c>
+      <c r="W25">
+        <f>SUM(Y11+Y15+Y19+Y23)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="S2:V3"/>
+    <mergeCell ref="W2:Z3"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="G9:G12"/>
+    <mergeCell ref="K9:K12"/>
+    <mergeCell ref="O9:O12"/>
+    <mergeCell ref="S9:S12"/>
+    <mergeCell ref="W9:W12"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="C13:C16"/>
+    <mergeCell ref="G13:G16"/>
+    <mergeCell ref="K13:K16"/>
+    <mergeCell ref="O13:O16"/>
+    <mergeCell ref="S13:S16"/>
+    <mergeCell ref="W13:W16"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="G17:G20"/>
+    <mergeCell ref="K17:K20"/>
+    <mergeCell ref="O17:O20"/>
+    <mergeCell ref="S17:S20"/>
+    <mergeCell ref="W17:W20"/>
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="C21:C24"/>
+    <mergeCell ref="G21:G24"/>
+    <mergeCell ref="K21:K24"/>
+    <mergeCell ref="O21:O24"/>
+    <mergeCell ref="S21:S24"/>
+    <mergeCell ref="W21:W24"/>
+    <mergeCell ref="A25:B25"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A4:A5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
